--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O602"/>
+  <dimension ref="A1:O606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31017,7 +31017,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>395.68</v>
+        <v>402.19</v>
       </c>
       <c r="C602" t="n">
         <v>449.19</v>
@@ -31056,6 +31056,210 @@
         <v>387.17</v>
       </c>
       <c r="O602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>405.95</v>
+      </c>
+      <c r="C603" t="n">
+        <v>447.82</v>
+      </c>
+      <c r="D603" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="E603" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="F603" t="n">
+        <v>366.87</v>
+      </c>
+      <c r="G603" t="n">
+        <v>371.77</v>
+      </c>
+      <c r="H603" t="n">
+        <v>377.48</v>
+      </c>
+      <c r="I603" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="J603" t="n">
+        <v>386.1</v>
+      </c>
+      <c r="K603" t="n">
+        <v>384.87</v>
+      </c>
+      <c r="L603" t="n">
+        <v>391.81</v>
+      </c>
+      <c r="M603" t="n">
+        <v>387.89</v>
+      </c>
+      <c r="N603" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>405.95</v>
+      </c>
+      <c r="C604" t="n">
+        <v>447.82</v>
+      </c>
+      <c r="D604" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="E604" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="F604" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="G604" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="H604" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="I604" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="J604" t="n">
+        <v>384.28</v>
+      </c>
+      <c r="K604" t="n">
+        <v>383.84</v>
+      </c>
+      <c r="L604" t="n">
+        <v>391.18</v>
+      </c>
+      <c r="M604" t="n">
+        <v>387.27</v>
+      </c>
+      <c r="N604" t="n">
+        <v>389.21</v>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>402.9</v>
+      </c>
+      <c r="C605" t="n">
+        <v>447.82</v>
+      </c>
+      <c r="D605" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="E605" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="F605" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="G605" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="H605" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="I605" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="J605" t="n">
+        <v>381.8</v>
+      </c>
+      <c r="K605" t="n">
+        <v>384.79</v>
+      </c>
+      <c r="L605" t="n">
+        <v>391.94</v>
+      </c>
+      <c r="M605" t="n">
+        <v>387.92</v>
+      </c>
+      <c r="N605" t="n">
+        <v>389.83</v>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>402.9</v>
+      </c>
+      <c r="C606" t="n">
+        <v>443.67</v>
+      </c>
+      <c r="D606" t="n">
+        <v>384.39</v>
+      </c>
+      <c r="E606" t="n">
+        <v>369.52</v>
+      </c>
+      <c r="F606" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="G606" t="n">
+        <v>369.37</v>
+      </c>
+      <c r="H606" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="I606" t="n">
+        <v>372.62</v>
+      </c>
+      <c r="J606" t="n">
+        <v>381.83</v>
+      </c>
+      <c r="K606" t="n">
+        <v>384.49</v>
+      </c>
+      <c r="L606" t="n">
+        <v>392.23</v>
+      </c>
+      <c r="M606" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="N606" t="n">
+        <v>389.65</v>
+      </c>
+      <c r="O606" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31072,7 +31276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B614"/>
+  <dimension ref="A1:B618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37215,6 +37419,46 @@
       </c>
       <c r="B614" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -37383,28 +37627,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2745425930964801</v>
+        <v>-0.3471398603219068</v>
       </c>
       <c r="J2" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K2" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006214515457419134</v>
+        <v>0.009774678431941908</v>
       </c>
       <c r="M2" t="n">
-        <v>19.31026733127767</v>
+        <v>19.48318221665687</v>
       </c>
       <c r="N2" t="n">
-        <v>628.5236552168542</v>
+        <v>642.035961049815</v>
       </c>
       <c r="O2" t="n">
-        <v>25.07037405418703</v>
+        <v>25.33842854341632</v>
       </c>
       <c r="P2" t="n">
-        <v>465.3492066196508</v>
+        <v>466.1699835524208</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37461,28 +37705,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08920300393781587</v>
+        <v>-0.1003200714934069</v>
       </c>
       <c r="J3" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K3" t="n">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001547688149851512</v>
+        <v>0.00198388555401019</v>
       </c>
       <c r="M3" t="n">
-        <v>12.76691399796283</v>
+        <v>12.72734827766123</v>
       </c>
       <c r="N3" t="n">
-        <v>266.1806095025303</v>
+        <v>264.8474265823035</v>
       </c>
       <c r="O3" t="n">
-        <v>16.31504243030125</v>
+        <v>16.27413366610658</v>
       </c>
       <c r="P3" t="n">
-        <v>457.1703434054185</v>
+        <v>457.2954456412234</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37539,28 +37783,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07361296248008294</v>
+        <v>-0.08882404707674373</v>
       </c>
       <c r="J4" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K4" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003232656539039258</v>
+        <v>0.004729846312781616</v>
       </c>
       <c r="M4" t="n">
-        <v>6.997097997556803</v>
+        <v>7.02010714870881</v>
       </c>
       <c r="N4" t="n">
-        <v>86.91175079638913</v>
+        <v>87.11356702650316</v>
       </c>
       <c r="O4" t="n">
-        <v>9.322647198966028</v>
+        <v>9.333464899302037</v>
       </c>
       <c r="P4" t="n">
-        <v>398.261203292723</v>
+        <v>398.4323254989036</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37617,28 +37861,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05561320046229593</v>
+        <v>-0.06755365800103312</v>
       </c>
       <c r="J5" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K5" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003616363769091469</v>
+        <v>0.005350473634412545</v>
       </c>
       <c r="M5" t="n">
-        <v>4.836480597332264</v>
+        <v>4.872514272492456</v>
       </c>
       <c r="N5" t="n">
-        <v>44.78168152652987</v>
+        <v>44.97311954652859</v>
       </c>
       <c r="O5" t="n">
-        <v>6.691911649635691</v>
+        <v>6.706200082500416</v>
       </c>
       <c r="P5" t="n">
-        <v>380.2969021795359</v>
+        <v>380.4301660577271</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37695,28 +37939,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1395826622124193</v>
+        <v>-0.1535293758594619</v>
       </c>
       <c r="J6" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K6" t="n">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04249269085862017</v>
+        <v>0.05031993540854163</v>
       </c>
       <c r="M6" t="n">
-        <v>3.654430788628661</v>
+        <v>3.698840234519089</v>
       </c>
       <c r="N6" t="n">
-        <v>22.85701978445535</v>
+        <v>23.36524002765953</v>
       </c>
       <c r="O6" t="n">
-        <v>4.780901566070499</v>
+        <v>4.833760443760068</v>
       </c>
       <c r="P6" t="n">
-        <v>379.4887257145575</v>
+        <v>379.6451440116161</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37773,28 +38017,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04418346552154211</v>
+        <v>-0.05800448779634088</v>
       </c>
       <c r="J7" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K7" t="n">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005464135781099166</v>
+        <v>0.009201833505000145</v>
       </c>
       <c r="M7" t="n">
-        <v>3.359385454551447</v>
+        <v>3.414303177777891</v>
       </c>
       <c r="N7" t="n">
-        <v>18.49895965229756</v>
+        <v>19.02760148712813</v>
       </c>
       <c r="O7" t="n">
-        <v>4.301041693857147</v>
+        <v>4.362063902228867</v>
       </c>
       <c r="P7" t="n">
-        <v>381.1975740071518</v>
+        <v>381.3525843031842</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37851,28 +38095,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02414933560666114</v>
+        <v>0.02037504148287331</v>
       </c>
       <c r="J8" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K8" t="n">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00279246528388355</v>
+        <v>0.002009889266893827</v>
       </c>
       <c r="M8" t="n">
-        <v>2.486375229164696</v>
+        <v>2.485392171904137</v>
       </c>
       <c r="N8" t="n">
-        <v>10.84268718260319</v>
+        <v>10.82682560947404</v>
       </c>
       <c r="O8" t="n">
-        <v>3.292823588138787</v>
+        <v>3.290414200290602</v>
       </c>
       <c r="P8" t="n">
-        <v>377.7156835341963</v>
+        <v>377.7580242812317</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37929,28 +38173,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06969030460411024</v>
+        <v>0.06062095421231167</v>
       </c>
       <c r="J9" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K9" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02608909563027861</v>
+        <v>0.01959271843236743</v>
       </c>
       <c r="M9" t="n">
-        <v>2.306196468519795</v>
+        <v>2.333883262079558</v>
       </c>
       <c r="N9" t="n">
-        <v>9.451700310779986</v>
+        <v>9.671068719783772</v>
       </c>
       <c r="O9" t="n">
-        <v>3.074361772918078</v>
+        <v>3.109834194902322</v>
       </c>
       <c r="P9" t="n">
-        <v>377.7035367842952</v>
+        <v>377.8052264514399</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38007,28 +38251,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008183517179178234</v>
+        <v>0.002919864742496305</v>
       </c>
       <c r="J10" t="n">
+        <v>605</v>
+      </c>
+      <c r="K10" t="n">
         <v>601</v>
       </c>
-      <c r="K10" t="n">
-        <v>597</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0003917703149837193</v>
+        <v>5.001440258656231e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.221971440970115</v>
+        <v>2.230482651207041</v>
       </c>
       <c r="N10" t="n">
-        <v>8.9320887726525</v>
+        <v>8.988292335514855</v>
       </c>
       <c r="O10" t="n">
-        <v>2.988660029620716</v>
+        <v>2.998048087592134</v>
       </c>
       <c r="P10" t="n">
-        <v>387.0800617253518</v>
+        <v>387.1390645207039</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38085,28 +38329,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01648864365465282</v>
+        <v>-0.02159560287595777</v>
       </c>
       <c r="J11" t="n">
+        <v>605</v>
+      </c>
+      <c r="K11" t="n">
         <v>601</v>
       </c>
-      <c r="K11" t="n">
-        <v>597</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.001300604330254473</v>
+        <v>0.002244982075705226</v>
       </c>
       <c r="M11" t="n">
-        <v>2.459985201924422</v>
+        <v>2.463426711224052</v>
       </c>
       <c r="N11" t="n">
-        <v>10.91274966470166</v>
+        <v>10.92975019429049</v>
       </c>
       <c r="O11" t="n">
-        <v>3.303445120582702</v>
+        <v>3.306017270718726</v>
       </c>
       <c r="P11" t="n">
-        <v>388.6288861393794</v>
+        <v>388.6861098332521</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38163,28 +38407,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.006530107889393767</v>
+        <v>0.003255256250682615</v>
       </c>
       <c r="J12" t="n">
+        <v>605</v>
+      </c>
+      <c r="K12" t="n">
         <v>601</v>
       </c>
-      <c r="K12" t="n">
-        <v>597</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.0001896257564216741</v>
+        <v>4.770815018062535e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5551600906715</v>
+        <v>2.551912701099892</v>
       </c>
       <c r="N12" t="n">
-        <v>11.75264890963344</v>
+        <v>11.7118524814012</v>
       </c>
       <c r="O12" t="n">
-        <v>3.428213661607665</v>
+        <v>3.4222583890468</v>
       </c>
       <c r="P12" t="n">
-        <v>393.9792859343331</v>
+        <v>394.0159763234747</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38241,28 +38485,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06252671337214878</v>
+        <v>0.05776371997980911</v>
       </c>
       <c r="J13" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K13" t="n">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01708669066930135</v>
+        <v>0.01474701596241024</v>
       </c>
       <c r="M13" t="n">
-        <v>2.475470208881536</v>
+        <v>2.479856890211055</v>
       </c>
       <c r="N13" t="n">
-        <v>11.70893099738893</v>
+        <v>11.7085724618862</v>
       </c>
       <c r="O13" t="n">
-        <v>3.421831526739581</v>
+        <v>3.421779136923685</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5322807527263</v>
+        <v>389.5856943172135</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38319,28 +38563,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03602025702927047</v>
+        <v>0.03944340158317059</v>
       </c>
       <c r="J14" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K14" t="n">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005799230157136792</v>
+        <v>0.007027195868993141</v>
       </c>
       <c r="M14" t="n">
-        <v>2.686455422973627</v>
+        <v>2.686578787528385</v>
       </c>
       <c r="N14" t="n">
-        <v>11.56882986355752</v>
+        <v>11.53462233758071</v>
       </c>
       <c r="O14" t="n">
-        <v>3.401298261481565</v>
+        <v>3.396265940349888</v>
       </c>
       <c r="P14" t="n">
-        <v>385.7481421864378</v>
+        <v>385.709674831453</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38378,7 +38622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O602"/>
+  <dimension ref="A1:O606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84470,7 +84714,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>-36.56188974822671,174.697310334885</t>
+          <t>-36.56190647906891,174.6973800449286</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -84534,6 +84778,314 @@
         </is>
       </c>
       <c r="O602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>-36.56191614233207,174.69742030757817</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>-36.562716560631166,174.69760109826478</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>-36.563229841497076,174.69664430572016</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>-36.56388191943725,174.69621076952518</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>-36.56452086996977,174.69577523743172</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>-36.56517050412639,174.69540654013966</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-36.565860448584665,174.69520315919164</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>-36.56654230794086,174.69492943525813</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>-36.56724242143927,174.69487092046646</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>-36.567943547065106,174.69481633841644</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>-36.56865420031025,174.69485171069593</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>-36.56934180356472,174.69484061862602</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>-36.57001483013434,174.69502514315224</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>-36.56191614233207,174.69742030757817</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>-36.562716560631166,174.69760109826478</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>-36.563229841497076,174.69664430572016</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>-36.56388191943725,174.69621076952518</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>-36.564514767389795,174.69576003350062</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>-36.565162809154245,174.69538292039195</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>-36.56585499219329,174.69517929618866</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>-36.56653855981231,174.694909753731</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>-36.56724047532105,174.69485072961203</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>-36.56794321979525,174.69480483748933</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>-36.568654247455164,174.6948446719507</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>-36.56934257248915,174.6948337572083</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>-36.57001249543686,174.69503777673205</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>-36.561908303781905,174.6973876477154</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>-36.562716560631166,174.69760109826478</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>-36.563229841497076,174.69664430572016</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>-36.56388191943725,174.69621076952518</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>-36.564514767389795,174.69576003350062</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>-36.565162809154245,174.69538292039195</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-36.56585499219329,174.69517929618866</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>-36.56653855981231,174.694909753731</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>-36.56723782346215,174.69482321680084</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>-36.56794352164612,174.69481544514053</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>-36.56865419058188,174.6948531631354</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>-36.56934176635868,174.6948409506301</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>-36.57001124758079,174.69504452916235</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>-36.561908303781905,174.6973876477154</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>-36.56270530188565,174.69755688440202</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>-36.56322635594703,174.6966306736646</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>-36.56387928147296,174.69620233146227</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>-36.56451360308155,174.69575713275088</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>-36.56516240415557,174.69538167724747</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>-36.56585332086525,174.69517198680103</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>-36.566538663351814,174.69491029741957</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>-36.56723785554113,174.6948235496171</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>-36.56794342632488,174.69481209535596</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>-36.568654168880066,174.69485640319272</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>-36.56934160513254,174.69484238931443</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>-36.57001160986161,174.69504256877937</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O606"/>
+  <dimension ref="A1:O608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31260,6 +31260,108 @@
         <v>389.65</v>
       </c>
       <c r="O606" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>404.01</v>
+      </c>
+      <c r="C607" t="n">
+        <v>441.55</v>
+      </c>
+      <c r="D607" t="n">
+        <v>384.41</v>
+      </c>
+      <c r="E607" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="F607" t="n">
+        <v>365.81</v>
+      </c>
+      <c r="G607" t="n">
+        <v>370.04</v>
+      </c>
+      <c r="H607" t="n">
+        <v>374.88</v>
+      </c>
+      <c r="I607" t="n">
+        <v>373.25</v>
+      </c>
+      <c r="J607" t="n">
+        <v>382.46</v>
+      </c>
+      <c r="K607" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="L607" t="n">
+        <v>393.05</v>
+      </c>
+      <c r="M607" t="n">
+        <v>388.75</v>
+      </c>
+      <c r="N607" t="n">
+        <v>389.94</v>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>404.54</v>
+      </c>
+      <c r="C608" t="n">
+        <v>440.21</v>
+      </c>
+      <c r="D608" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="E608" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="F608" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="G608" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="H608" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="I608" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="J608" t="n">
+        <v>382.18</v>
+      </c>
+      <c r="K608" t="n">
+        <v>385.66</v>
+      </c>
+      <c r="L608" t="n">
+        <v>393.49</v>
+      </c>
+      <c r="M608" t="n">
+        <v>389.14</v>
+      </c>
+      <c r="N608" t="n">
+        <v>390.68</v>
+      </c>
+      <c r="O608" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31276,7 +31378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B618"/>
+  <dimension ref="A1:B620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37459,6 +37561,26 @@
       </c>
       <c r="B618" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -37627,28 +37749,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3471398603219068</v>
+        <v>-0.3837504874203402</v>
       </c>
       <c r="J2" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K2" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009774678431941908</v>
+        <v>0.01184056663444022</v>
       </c>
       <c r="M2" t="n">
-        <v>19.48318221665687</v>
+        <v>19.57717072312585</v>
       </c>
       <c r="N2" t="n">
-        <v>642.035961049815</v>
+        <v>649.0995505758577</v>
       </c>
       <c r="O2" t="n">
-        <v>25.33842854341632</v>
+        <v>25.47743218175367</v>
       </c>
       <c r="P2" t="n">
-        <v>466.1699835524208</v>
+        <v>466.5852958390344</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37705,28 +37827,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1003200714934069</v>
+        <v>-0.1098258920177154</v>
       </c>
       <c r="J3" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K3" t="n">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00198388555401019</v>
+        <v>0.002389478290725</v>
       </c>
       <c r="M3" t="n">
-        <v>12.72734827766123</v>
+        <v>12.72361507745677</v>
       </c>
       <c r="N3" t="n">
-        <v>264.8474265823035</v>
+        <v>264.5864873703754</v>
       </c>
       <c r="O3" t="n">
-        <v>16.27413366610658</v>
+        <v>16.2661146980579</v>
       </c>
       <c r="P3" t="n">
-        <v>457.2954456412234</v>
+        <v>457.4027560117258</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37783,28 +37905,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08882404707674373</v>
+        <v>-0.09744290108153898</v>
       </c>
       <c r="J4" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K4" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004729846312781616</v>
+        <v>0.005697099064548516</v>
       </c>
       <c r="M4" t="n">
-        <v>7.02010714870881</v>
+        <v>7.035867952241022</v>
       </c>
       <c r="N4" t="n">
-        <v>87.11356702650316</v>
+        <v>87.3337440160568</v>
       </c>
       <c r="O4" t="n">
-        <v>9.333464899302037</v>
+        <v>9.345252485409734</v>
       </c>
       <c r="P4" t="n">
-        <v>398.4323254989036</v>
+        <v>398.5296149128838</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37861,28 +37983,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06755365800103312</v>
+        <v>-0.07356365678587437</v>
       </c>
       <c r="J5" t="n">
+        <v>607</v>
+      </c>
+      <c r="K5" t="n">
         <v>605</v>
       </c>
-      <c r="K5" t="n">
-        <v>603</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.005350473634412545</v>
+        <v>0.006351593475969919</v>
       </c>
       <c r="M5" t="n">
-        <v>4.872514272492456</v>
+        <v>4.891147524683634</v>
       </c>
       <c r="N5" t="n">
-        <v>44.97311954652859</v>
+        <v>45.07504933913653</v>
       </c>
       <c r="O5" t="n">
-        <v>6.706200082500416</v>
+        <v>6.71379544960498</v>
       </c>
       <c r="P5" t="n">
-        <v>380.4301660577271</v>
+        <v>380.4974681344968</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37939,28 +38061,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1535293758594619</v>
+        <v>-0.1602517909934803</v>
       </c>
       <c r="J6" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K6" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05031993540854163</v>
+        <v>0.05429335885535669</v>
       </c>
       <c r="M6" t="n">
-        <v>3.698840234519089</v>
+        <v>3.719613919313365</v>
       </c>
       <c r="N6" t="n">
-        <v>23.36524002765953</v>
+        <v>23.59742001647465</v>
       </c>
       <c r="O6" t="n">
-        <v>4.833760443760068</v>
+        <v>4.857717572736671</v>
       </c>
       <c r="P6" t="n">
-        <v>379.6451440116161</v>
+        <v>379.7207898104513</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38017,28 +38139,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05800448779634088</v>
+        <v>-0.06510094170884959</v>
       </c>
       <c r="J7" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K7" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009201833505000145</v>
+        <v>0.01144549061664613</v>
       </c>
       <c r="M7" t="n">
-        <v>3.414303177777891</v>
+        <v>3.442660370560426</v>
       </c>
       <c r="N7" t="n">
-        <v>19.02760148712813</v>
+        <v>19.31033284528789</v>
       </c>
       <c r="O7" t="n">
-        <v>4.362063902228867</v>
+        <v>4.394352380645855</v>
       </c>
       <c r="P7" t="n">
-        <v>381.3525843031842</v>
+        <v>381.4324419730923</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38095,28 +38217,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02037504148287331</v>
+        <v>0.01718503234876711</v>
       </c>
       <c r="J8" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K8" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002009889266893827</v>
+        <v>0.00143180435996404</v>
       </c>
       <c r="M8" t="n">
-        <v>2.485392171904137</v>
+        <v>2.490474979911312</v>
       </c>
       <c r="N8" t="n">
-        <v>10.82682560947404</v>
+        <v>10.86535116531997</v>
       </c>
       <c r="O8" t="n">
-        <v>3.290414200290602</v>
+        <v>3.296263212384589</v>
       </c>
       <c r="P8" t="n">
-        <v>377.7580242812317</v>
+        <v>377.7939278707476</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38173,28 +38295,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06062095421231167</v>
+        <v>0.05632886693699431</v>
       </c>
       <c r="J9" t="n">
+        <v>607</v>
+      </c>
+      <c r="K9" t="n">
         <v>605</v>
       </c>
-      <c r="K9" t="n">
-        <v>603</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01959271843236743</v>
+        <v>0.01687298851745211</v>
       </c>
       <c r="M9" t="n">
-        <v>2.333883262079558</v>
+        <v>2.347150318785699</v>
       </c>
       <c r="N9" t="n">
-        <v>9.671068719783772</v>
+        <v>9.765425764337479</v>
       </c>
       <c r="O9" t="n">
-        <v>3.109834194902322</v>
+        <v>3.124968122131405</v>
       </c>
       <c r="P9" t="n">
-        <v>377.8052264514399</v>
+        <v>377.853511219656</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38251,28 +38373,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002919864742496305</v>
+        <v>-0.0004593456741641529</v>
       </c>
       <c r="J10" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K10" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L10" t="n">
-        <v>5.001440258656231e-05</v>
+        <v>1.236519591385488e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>2.230482651207041</v>
+        <v>2.238374042482535</v>
       </c>
       <c r="N10" t="n">
-        <v>8.988292335514855</v>
+        <v>9.037152237942005</v>
       </c>
       <c r="O10" t="n">
-        <v>2.998048087592134</v>
+        <v>3.006185662586728</v>
       </c>
       <c r="P10" t="n">
-        <v>387.1390645207039</v>
+        <v>387.1770586648198</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38329,28 +38451,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02159560287595777</v>
+        <v>-0.02359969920978749</v>
       </c>
       <c r="J11" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K11" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002244982075705226</v>
+        <v>0.002693382392993882</v>
       </c>
       <c r="M11" t="n">
-        <v>2.463426711224052</v>
+        <v>2.46309671291012</v>
       </c>
       <c r="N11" t="n">
-        <v>10.92975019429049</v>
+        <v>10.92188236486315</v>
       </c>
       <c r="O11" t="n">
-        <v>3.306017270718726</v>
+        <v>3.304827130859215</v>
       </c>
       <c r="P11" t="n">
-        <v>388.6861098332521</v>
+        <v>388.7086394939872</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38407,28 +38529,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.003255256250682615</v>
+        <v>0.002681074377389321</v>
       </c>
       <c r="J12" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K12" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L12" t="n">
-        <v>4.770815018062535e-05</v>
+        <v>3.260499824053742e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>2.551912701099892</v>
+        <v>2.545912232178833</v>
       </c>
       <c r="N12" t="n">
-        <v>11.7118524814012</v>
+        <v>11.67544004517118</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4222583890468</v>
+        <v>3.41693430507102</v>
       </c>
       <c r="P12" t="n">
-        <v>394.0159763234747</v>
+        <v>394.0224306260066</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38485,28 +38607,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05776371997980911</v>
+        <v>0.05623973857214108</v>
       </c>
       <c r="J13" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K13" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01474701596241024</v>
+        <v>0.01407713503396046</v>
       </c>
       <c r="M13" t="n">
-        <v>2.479856890211055</v>
+        <v>2.478321113298157</v>
       </c>
       <c r="N13" t="n">
-        <v>11.7085724618862</v>
+        <v>11.68595631788455</v>
       </c>
       <c r="O13" t="n">
-        <v>3.421779136923685</v>
+        <v>3.418472804906389</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5856943172135</v>
+        <v>389.6028420575193</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38563,28 +38685,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03944340158317059</v>
+        <v>0.04188737287717784</v>
       </c>
       <c r="J14" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K14" t="n">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007027195868993141</v>
+        <v>0.007950066930576427</v>
       </c>
       <c r="M14" t="n">
-        <v>2.686578787528385</v>
+        <v>2.690459660714903</v>
       </c>
       <c r="N14" t="n">
-        <v>11.53462233758071</v>
+        <v>11.53773243128731</v>
       </c>
       <c r="O14" t="n">
-        <v>3.396265940349888</v>
+        <v>3.396723779068193</v>
       </c>
       <c r="P14" t="n">
-        <v>385.709674831453</v>
+        <v>385.6821207510013</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38622,7 +38744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O606"/>
+  <dimension ref="A1:O608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85091,6 +85213,160 @@
         </is>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>-36.561911156501196,174.6973995337631</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>-36.56269955042364,174.69753429804794</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>-36.56322641040878,174.69663088666545</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>-36.56388055160399,174.69620639423323</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>-36.56451661422343,174.69576463469005</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>-36.56516466539798,174.6953886181377</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>-36.56585405821591,174.69517521153082</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>-36.566539967949396,174.69491714789567</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>-36.56723852919942,174.6948305387585</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>-36.56794350258188,174.69481477518363</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>-36.568654107515854,174.69486556473407</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>-36.569340736991464,174.69485013607616</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>-36.57001102618692,174.69504572717415</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>-36.561912518610015,174.69740520908346</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>-36.562695915063316,174.69752002176915</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>-36.56322202623812,174.6966137400972</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>-36.56388012822701,174.6962050399762</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>-36.56451617258931,174.69576353440561</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>-36.565161087909814,174.69537763702797</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>-36.56584820856482,174.69514962867592</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>-36.56653988511781,174.6949167129448</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>-36.56723822979578,174.69482743247343</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>-36.56794379807716,174.69482515951591</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>-36.56865407458844,174.69487048068308</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>-36.56934025331265,174.69485445212902</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>-36.57000953680973,174.69505378652605</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O608"/>
+  <dimension ref="A1:O609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31323,7 +31323,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>404.54</v>
+        <v>410.64</v>
       </c>
       <c r="C608" t="n">
         <v>440.21</v>
@@ -31362,6 +31362,57 @@
         <v>390.68</v>
       </c>
       <c r="O608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>417.23</v>
+      </c>
+      <c r="C609" t="n">
+        <v>436.86</v>
+      </c>
+      <c r="D609" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="E609" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="F609" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="G609" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="H609" t="n">
+        <v>372.94</v>
+      </c>
+      <c r="I609" t="n">
+        <v>372.99</v>
+      </c>
+      <c r="J609" t="n">
+        <v>381.93</v>
+      </c>
+      <c r="K609" t="n">
+        <v>385.98</v>
+      </c>
+      <c r="L609" t="n">
+        <v>393.74</v>
+      </c>
+      <c r="M609" t="n">
+        <v>389.68</v>
+      </c>
+      <c r="N609" t="n">
+        <v>391.38</v>
+      </c>
+      <c r="O609" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31378,7 +31429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B620"/>
+  <dimension ref="A1:B621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37581,6 +37632,16 @@
       </c>
       <c r="B620" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -37749,28 +37810,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3837504874203402</v>
+        <v>-0.3952412315487101</v>
       </c>
       <c r="J2" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K2" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01184056663444022</v>
+        <v>0.01256918478535873</v>
       </c>
       <c r="M2" t="n">
-        <v>19.57717072312585</v>
+        <v>19.5951292388319</v>
       </c>
       <c r="N2" t="n">
-        <v>649.0995505758577</v>
+        <v>649.5520617670453</v>
       </c>
       <c r="O2" t="n">
-        <v>25.47743218175367</v>
+        <v>25.48631126246098</v>
       </c>
       <c r="P2" t="n">
-        <v>466.5852958390344</v>
+        <v>466.716166131466</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37827,28 +37888,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1098258920177154</v>
+        <v>-0.1159343762080505</v>
       </c>
       <c r="J3" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K3" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002389478290725</v>
+        <v>0.002667129396011325</v>
       </c>
       <c r="M3" t="n">
-        <v>12.72361507745677</v>
+        <v>12.72727136853864</v>
       </c>
       <c r="N3" t="n">
-        <v>264.5864873703754</v>
+        <v>264.6561846494885</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2661146980579</v>
+        <v>16.26825696408464</v>
       </c>
       <c r="P3" t="n">
-        <v>457.4027560117258</v>
+        <v>457.4719452097459</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37905,28 +37966,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09744290108153898</v>
+        <v>-0.1012937626343535</v>
       </c>
       <c r="J4" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K4" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005697099064548516</v>
+        <v>0.006162871964183303</v>
       </c>
       <c r="M4" t="n">
-        <v>7.035867952241022</v>
+        <v>7.041604346112612</v>
       </c>
       <c r="N4" t="n">
-        <v>87.3337440160568</v>
+        <v>87.39125798518114</v>
       </c>
       <c r="O4" t="n">
-        <v>9.345252485409734</v>
+        <v>9.348329154730333</v>
       </c>
       <c r="P4" t="n">
-        <v>398.5296149128838</v>
+        <v>398.5732295336035</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37983,28 +38044,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07356365678587437</v>
+        <v>-0.07656005447832141</v>
       </c>
       <c r="J5" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K5" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006351593475969919</v>
+        <v>0.006883318423558937</v>
       </c>
       <c r="M5" t="n">
-        <v>4.891147524683634</v>
+        <v>4.900721049438214</v>
       </c>
       <c r="N5" t="n">
-        <v>45.07504933913653</v>
+        <v>45.12509535699433</v>
       </c>
       <c r="O5" t="n">
-        <v>6.71379544960498</v>
+        <v>6.71752151890817</v>
       </c>
       <c r="P5" t="n">
-        <v>380.4974681344968</v>
+        <v>380.5311378324328</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38061,28 +38122,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1602517909934803</v>
+        <v>-0.1634834065891829</v>
       </c>
       <c r="J6" t="n">
+        <v>608</v>
+      </c>
+      <c r="K6" t="n">
         <v>607</v>
       </c>
-      <c r="K6" t="n">
-        <v>606</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.05429335885535669</v>
+        <v>0.0562644778563256</v>
       </c>
       <c r="M6" t="n">
-        <v>3.719613919313365</v>
+        <v>3.729346654420216</v>
       </c>
       <c r="N6" t="n">
-        <v>23.59742001647465</v>
+        <v>23.70132113765571</v>
       </c>
       <c r="O6" t="n">
-        <v>4.857717572736671</v>
+        <v>4.868400264733346</v>
       </c>
       <c r="P6" t="n">
-        <v>379.7207898104513</v>
+        <v>379.7572777628894</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38139,28 +38200,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06510094170884959</v>
+        <v>-0.06913427305857603</v>
       </c>
       <c r="J7" t="n">
+        <v>608</v>
+      </c>
+      <c r="K7" t="n">
         <v>607</v>
       </c>
-      <c r="K7" t="n">
-        <v>606</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01144549061664613</v>
+        <v>0.0127923192685796</v>
       </c>
       <c r="M7" t="n">
-        <v>3.442660370560426</v>
+        <v>3.459450039490359</v>
       </c>
       <c r="N7" t="n">
-        <v>19.31033284528789</v>
+        <v>19.50092557918317</v>
       </c>
       <c r="O7" t="n">
-        <v>4.394352380645855</v>
+        <v>4.415985233125579</v>
       </c>
       <c r="P7" t="n">
-        <v>381.4324419730923</v>
+        <v>381.4779820437157</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38217,28 +38278,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01718503234876711</v>
+        <v>0.01534382265051309</v>
       </c>
       <c r="J8" t="n">
+        <v>608</v>
+      </c>
+      <c r="K8" t="n">
         <v>607</v>
       </c>
-      <c r="K8" t="n">
-        <v>606</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.00143180435996404</v>
+        <v>0.001141303243052949</v>
       </c>
       <c r="M8" t="n">
-        <v>2.490474979911312</v>
+        <v>2.49413227795185</v>
       </c>
       <c r="N8" t="n">
-        <v>10.86535116531997</v>
+        <v>10.8937983527971</v>
       </c>
       <c r="O8" t="n">
-        <v>3.296263212384589</v>
+        <v>3.300575457825059</v>
       </c>
       <c r="P8" t="n">
-        <v>377.7939278707476</v>
+        <v>377.8147168445314</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38295,28 +38356,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05632886693699431</v>
+        <v>0.05411708986177404</v>
       </c>
       <c r="J9" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K9" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01687298851745211</v>
+        <v>0.01554833657548094</v>
       </c>
       <c r="M9" t="n">
-        <v>2.347150318785699</v>
+        <v>2.35427156548522</v>
       </c>
       <c r="N9" t="n">
-        <v>9.765425764337479</v>
+        <v>9.816321599134776</v>
       </c>
       <c r="O9" t="n">
-        <v>3.124968122131405</v>
+        <v>3.133100955784026</v>
       </c>
       <c r="P9" t="n">
-        <v>377.853511219656</v>
+        <v>377.8784777205329</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38373,28 +38434,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0004593456741641529</v>
+        <v>-0.002270422463957916</v>
       </c>
       <c r="J10" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K10" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L10" t="n">
-        <v>1.236519591385488e-06</v>
+        <v>3.017378012115657e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.238374042482535</v>
+        <v>2.242966478500164</v>
       </c>
       <c r="N10" t="n">
-        <v>9.037152237942005</v>
+        <v>9.067295711406356</v>
       </c>
       <c r="O10" t="n">
-        <v>3.006185662586728</v>
+        <v>3.011195063659336</v>
       </c>
       <c r="P10" t="n">
-        <v>387.1770586648198</v>
+        <v>387.1974907164456</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38451,28 +38512,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02359969920978749</v>
+        <v>-0.02432269925894318</v>
       </c>
       <c r="J11" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K11" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002693382392993882</v>
+        <v>0.002869582224865885</v>
       </c>
       <c r="M11" t="n">
-        <v>2.46309671291012</v>
+        <v>2.461868333131659</v>
       </c>
       <c r="N11" t="n">
-        <v>10.92188236486315</v>
+        <v>10.91098820458388</v>
       </c>
       <c r="O11" t="n">
-        <v>3.304827130859215</v>
+        <v>3.303178500260602</v>
       </c>
       <c r="P11" t="n">
-        <v>388.7086394939872</v>
+        <v>388.7167961742632</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38529,28 +38590,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002681074377389321</v>
+        <v>0.002557539571069472</v>
       </c>
       <c r="J12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K12" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="L12" t="n">
-        <v>3.260499824053742e-05</v>
+        <v>2.978362761696385e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>2.545912232178833</v>
+        <v>2.54222174550387</v>
       </c>
       <c r="N12" t="n">
-        <v>11.67544004517118</v>
+        <v>11.65631970941046</v>
       </c>
       <c r="O12" t="n">
-        <v>3.41693430507102</v>
+        <v>3.41413527989306</v>
       </c>
       <c r="P12" t="n">
-        <v>394.0224306260066</v>
+        <v>394.0238243104459</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38607,28 +38668,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05623973857214108</v>
+        <v>0.05573747709971991</v>
       </c>
       <c r="J13" t="n">
+        <v>608</v>
+      </c>
+      <c r="K13" t="n">
         <v>607</v>
       </c>
-      <c r="K13" t="n">
-        <v>606</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.01407713503396046</v>
+        <v>0.01387897718406006</v>
       </c>
       <c r="M13" t="n">
-        <v>2.478321113298157</v>
+        <v>2.476411794314272</v>
       </c>
       <c r="N13" t="n">
-        <v>11.68595631788455</v>
+        <v>11.670153205093</v>
       </c>
       <c r="O13" t="n">
-        <v>3.418472804906389</v>
+        <v>3.416160594160205</v>
       </c>
       <c r="P13" t="n">
-        <v>389.6028420575193</v>
+        <v>389.6085130577279</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38685,28 +38746,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04188737287717784</v>
+        <v>0.04347042456134345</v>
       </c>
       <c r="J14" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K14" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007950066930576427</v>
+        <v>0.008564640217114339</v>
       </c>
       <c r="M14" t="n">
-        <v>2.690459660714903</v>
+        <v>2.694365376206631</v>
       </c>
       <c r="N14" t="n">
-        <v>11.53773243128731</v>
+        <v>11.55290783374385</v>
       </c>
       <c r="O14" t="n">
-        <v>3.396723779068193</v>
+        <v>3.398956874357757</v>
       </c>
       <c r="P14" t="n">
-        <v>385.6821207510013</v>
+        <v>385.6642136995383</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38744,7 +38805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O608"/>
+  <dimension ref="A1:O609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85298,7 +85359,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>-36.561912518610015,174.69740520908346</t>
+          <t>-36.5619281956914,174.69747052882195</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -85362,6 +85423,83 @@
         </is>
       </c>
       <c r="O608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-36.561945132038296,174.69754109558409</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>-36.562686826654875,174.69748433107782</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>-36.56322749964332,174.69663514668267</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>-36.563880160794454,174.69620514414984</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-36.56451749749162,174.695766835259</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>-36.56515781416975,174.69536758827746</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>-36.56584929001335,174.69515435827907</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>-36.566539429544086,174.69491432071504</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>-36.56723796247105,174.6948246590046</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>-36.567943899752734,174.6948287326195</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>-36.56865405587959,174.69487327383592</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>-36.56933958360326,174.69486042820216</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>-36.570008127938905,174.695061410237</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
